--- a/BA_Selection_Criteria_DPR_Logistics_Editable_BlackFix.xlsx
+++ b/BA_Selection_Criteria_DPR_Logistics_Editable_BlackFix.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Arial"/>
       <sz val="10"/>
@@ -61,6 +61,17 @@
       <name val="Arial"/>
       <color rgb="FF000000"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="12">
@@ -131,7 +142,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -231,12 +242,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -317,6 +333,13 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1440,6 +1463,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>64</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2667000" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2087,7 +2140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="10.2"/>
   <cols>
     <col hidden="1" width="13" customWidth="1" style="1" min="1" max="2"/>
@@ -3474,7 +3527,18 @@
         </is>
       </c>
     </row>
-    <row r="64" hidden="1"/>
+    <row r="64" hidden="1">
+      <c r="D64" s="38" t="n"/>
+      <c r="E64" s="38" t="n"/>
+      <c r="F64" s="38" t="n"/>
+      <c r="G64" s="38" t="n"/>
+    </row>
+    <row r="65">
+      <c r="D65" s="39" t="n"/>
+    </row>
+    <row r="66">
+      <c r="D66" s="40" t="n"/>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="0" algorithmName="SHA-512" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" saltValue="ZbnqAzubMniPzK1WjE1S/A==" formatRows="1" sort="1" spinCount="100000" hashValue="gji0+F0JPqDy+sNtjBFccVBfZqN+TQ13o3bb+Gl3GKOLcPsgdLM1FhEBKjfQnhhR5cFlwu0w0AcHAnVDQF8jjQ=="/>
   <mergeCells count="9">
@@ -3531,6 +3595,7 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
